--- a/data/transTeams.xlsx
+++ b/data/transTeams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jarda\Documents\.My Life\Programovani\JS\betCompare2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FB44E5-059B-4E61-97BB-0AA0131F5F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6337CDC1-8CC4-40EF-A2B2-84C16AE5F277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{E046BDE1-62B3-4E90-B22D-F0278834E5F0}"/>
   </bookViews>
@@ -6857,6 +6857,7 @@
   <cols>
     <col min="2" max="2" width="19.8984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -12641,6 +12642,7 @@
   <autoFilter ref="A1:D525" xr:uid="{F1E16FBF-87B3-497F-8EDE-437FBA57A6FB}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
